--- a/Docs/Spriint Backlog.xlsx
+++ b/Docs/Spriint Backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0d25a1f11c8555b/Desktop/SpaceLandMapper Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_84757D8ED345785E610C28944F5DCE3A7744A162" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33B42B51-4AB6-46A8-8562-EE6010BC187C}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_84757D8ED345785E610C28944F5DCE3A7744A162" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D94410E4-9EE1-49C2-96D9-44684B8C27E5}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -243,7 +243,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -336,18 +336,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -367,6 +367,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -668,7 +672,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
@@ -727,7 +731,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="7"/>
@@ -837,7 +841,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B9" s="7"/>
@@ -915,7 +919,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="7"/>
@@ -993,7 +997,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="7"/>
@@ -1071,7 +1075,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>50</v>
       </c>
       <c r="B18" s="7"/>
@@ -1149,7 +1153,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B21" s="7"/>
@@ -1259,7 +1263,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B25" s="7"/>
